--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123608753</v>
+        <v>123608438</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>79890</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backbodarna, Backbodarna, Ång</t>
+          <t>Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557803</v>
+        <v>557872</v>
       </c>
       <c r="R2" t="n">
-        <v>7043520</v>
+        <v>7043489</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +790,7 @@
         <v>123608469</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608438</v>
+        <v>123608753</v>
       </c>
       <c r="B4" t="n">
-        <v>79884</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,41 +920,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backbodarna, Ång</t>
+          <t>Backbodarna, Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557872</v>
+        <v>557803</v>
       </c>
       <c r="R4" t="n">
-        <v>7043489</v>
+        <v>7043520</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123608438</v>
       </c>
       <c r="B2" t="n">
-        <v>79890</v>
+        <v>79895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608469</v>
+        <v>123608753</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,22 +827,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backbodarna, Ång</t>
+          <t>Backbodarna, Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557872</v>
+        <v>557803</v>
       </c>
       <c r="R3" t="n">
-        <v>7043489</v>
+        <v>7043520</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608753</v>
+        <v>123608469</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,22 +948,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backbodarna, Backbodarna, Ång</t>
+          <t>Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557803</v>
+        <v>557872</v>
       </c>
       <c r="R4" t="n">
-        <v>7043520</v>
+        <v>7043489</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123608438</v>
+        <v>123608753</v>
       </c>
       <c r="B2" t="n">
-        <v>79895</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backbodarna, Ång</t>
+          <t>Backbodarna, Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557872</v>
+        <v>557803</v>
       </c>
       <c r="R2" t="n">
-        <v>7043489</v>
+        <v>7043520</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608753</v>
+        <v>123608469</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,22 +836,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backbodarna, Backbodarna, Ång</t>
+          <t>Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557803</v>
+        <v>557872</v>
       </c>
       <c r="R3" t="n">
-        <v>7043520</v>
+        <v>7043489</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608469</v>
+        <v>123608438</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79897</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +929,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608469</v>
+        <v>123608438</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608438</v>
+        <v>123608469</v>
       </c>
       <c r="B4" t="n">
-        <v>79897</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,28 +920,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608438</v>
+        <v>123608469</v>
       </c>
       <c r="B3" t="n">
-        <v>79897</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,28 +808,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608469</v>
+        <v>123608438</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +929,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123608753</v>
+        <v>123608469</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,22 +715,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backbodarna, Backbodarna, Ång</t>
+          <t>Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557803</v>
+        <v>557872</v>
       </c>
       <c r="R2" t="n">
-        <v>7043520</v>
+        <v>7043489</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608469</v>
+        <v>123608753</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -836,22 +836,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backbodarna, Ång</t>
+          <t>Backbodarna, Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557872</v>
+        <v>557803</v>
       </c>
       <c r="R3" t="n">
-        <v>7043489</v>
+        <v>7043520</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 50751-2024 artfynd.xlsx
+++ b/artfynd/A 50751-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123608469</v>
+        <v>123608753</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,22 +715,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backbodarna, Ång</t>
+          <t>Backbodarna, Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557872</v>
+        <v>557803</v>
       </c>
       <c r="R2" t="n">
-        <v>7043489</v>
+        <v>7043520</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123608753</v>
+        <v>123608438</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backbodarna, Backbodarna, Ång</t>
+          <t>Backbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557803</v>
+        <v>557872</v>
       </c>
       <c r="R3" t="n">
-        <v>7043520</v>
+        <v>7043489</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123608438</v>
+        <v>123608469</v>
       </c>
       <c r="B4" t="n">
-        <v>79897</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,28 +920,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Backbodarna, Ång</t>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
